--- a/output/2026-10-04_20_Malesia_Selangor_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-10-04_20_Malesia_Selangor_Impiantistica_aspirazione_industriale.xlsx
@@ -503,7 +503,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Verificata su exporthub.com (profilo attivo, sede Shah Alam, azienda storica dal 1970). Nessun sito ufficiale proprio o contatto diretto reperito in fonti pubbliche: campi lasciati vuoti.</t>
+          <t>Verificata su exporthub.com (profilo attivo, sede Shah Alam, azienda storica dal 1970). Nessun sito ufficiale proprio o contatto diretto reperito in fonti pubbliche: campi lasciati vuoti. [DUPLICATO — vedi anche: 2026-10-01_01_Malesia_Kedah_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Confermata tramite fetch diretto del sito ufficiale e fonti matrade.gov.my / AHK Malaysia directory. HQ a Seri Kembangan, Selangor; filiali a Penang, Johor, Singapore.</t>
+          <t>Confermata tramite fetch diretto del sito ufficiale e fonti matrade.gov.my / AHK Malaysia directory. HQ a Seri Kembangan, Selangor; filiali a Penang, Johor, Singapore. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -583,7 +583,7 @@
       <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Confermata tramite fetch diretto del sito ufficiale e certificazioni BSI (ISO 9001, EN 12101-3). Il vecchio dominio eltafans.asia reindirizza ora a elta.asia. Email non reperita.</t>
+          <t>Confermata tramite fetch diretto del sito ufficiale e certificazioni BSI (ISO 9001, EN 12101-3). Il vecchio dominio eltafans.asia reindirizza ora a elta.asia. Email non reperita. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Confermata tramite mdbc.com.my directory e fonti di settore (wattagnet.com). GM locale: Mohamed Maqbool (+6012-683 8488).</t>
+          <t>Confermata tramite mdbc.com.my directory e fonti di settore (wattagnet.com). GM locale: Mohamed Maqbool (+6012-683 8488). [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -655,7 +655,7 @@
       <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Confermata su machinetools.com con indirizzo completo (Jalan Utarid U5/22, Mah Sing Industrial Area, Shah Alam). Nessun contatto diretto reperito pubblicamente.</t>
+          <t>Confermata su machinetools.com con indirizzo completo (Jalan Utarid U5/22, Mah Sing Industrial Area, Shah Alam). Nessun contatto diretto reperito pubblicamente. [DUPLICATO — vedi anche: 2026-10-03_17_Malesia_Perlis_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Confermata tramite piu' fonti (careerconnect.mmu.edu.my, craft.co, matrade.gov.my). Focus principale su filtrazione cleanroom/HVAC, segmento adiacente al settore target. Email reperita risultava troncata/non affidabile: lasciata vuota.</t>
+          <t>Confermata tramite piu' fonti (careerconnect.mmu.edu.my, craft.co, matrade.gov.my). Focus principale su filtrazione cleanroom/HVAC, segmento adiacente al settore target. Email reperita risultava troncata/non affidabile: lasciata vuota. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Confermata tramite fetch diretto del sito ufficiale (pagina dedicata Fans &amp; Ventilation e Blower Fans). Attiva dal 1977, sede storica a Petaling Jaya, Selangor. Email alternativa: sales@cthardware.com.</t>
+          <t>Confermata tramite fetch diretto del sito ufficiale (pagina dedicata Fans &amp; Ventilation e Blower Fans). Attiva dal 1977, sede storica a Petaling Jaya, Selangor. Email alternativa: sales@cthardware.com. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Confermata tramite pagina contatti ufficiale systemair.com/en-my/contact. Direttore locale: Eric Tan. Email generica non reperita pubblicamente.</t>
+          <t>Confermata tramite pagina contatti ufficiale systemair.com/en-my/contact. Direttore locale: Eric Tan. Email generica non reperita pubblicamente. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Confermata tramite bulkinside.com (directory produttori di settore bulk material handling). Indirizzo: Unit 3.037, 129 Offices, Jaya One, Petaling Jaya. Prodotto: dust suppression meccanico passivo, segmento adiacente ma pertinente al settore target. Nessun dominio web ufficiale proprio confermato.</t>
+          <t>Confermata tramite bulkinside.com (directory produttori di settore bulk material handling). Indirizzo: Unit 3.037, 129 Offices, Jaya One, Petaling Jaya. Prodotto: dust suppression meccanico passivo, segmento adiacente ma pertinente al settore target. Nessun dominio web ufficiale proprio confermato. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
